--- a/output/2026-10-01_02_Malesia_Kedah_Componentistica_Ventilazione_industriale.xlsx
+++ b/output/2026-10-01_02_Malesia_Kedah_Componentistica_Ventilazione_industriale.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Specialista cooling tower (ricambi, vendita, installazione, riparazione); offre anche aria condizionata e ventilazione, cuscinetti, pompe. Focus primario su cooling tower, borderline rispetto al target.</t>
+          <t>Specialista cooling tower (ricambi, vendita, installazione, riparazione); offre anche aria condizionata e ventilazione, cuscinetti, pompe. Focus primario su cooling tower, borderline rispetto al target. [DUPLICATO — vedi anche: 2026-10-01_01_Malesia_Kedah_Impiantistica_aspirazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -516,7 +516,6 @@
           <t>Agro-Industrial Supplies (M) Sdn. Bhd.</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>Jitra, Kedah</t>
@@ -623,7 +622,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Distributore esclusivo ventole/blower Nicotra Gebhardt in Malaysia, con copertura dichiarata su tutto il territorio incl. Kedah.</t>
+          <t>Distributore esclusivo ventole/blower Nicotra Gebhardt in Malaysia, con copertura dichiarata su tutto il territorio incl. Kedah. [DUPLICATO — vedi anche: 2026-10-01_01_Malesia_Kedah_Impiantistica_aspirazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -665,7 +664,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Distributore esclusivo brand taiwanese KOLOWA in Malaysia; progettazione, fornitura e installazione sistemi di ventilazione industriale, copertura nazionale.</t>
+          <t>Distributore esclusivo brand taiwanese KOLOWA in Malaysia; progettazione, fornitura e installazione sistemi di ventilazione industriale, copertura nazionale. [DUPLICATO — vedi anche: 2026-10-01_01_Malesia_Kedah_Impiantistica_aspirazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">

--- a/output/2026-10-01_02_Malesia_Kedah_Componentistica_Ventilazione_industriale.xlsx
+++ b/output/2026-10-01_02_Malesia_Kedah_Componentistica_Ventilazione_industriale.xlsx
@@ -585,7 +585,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>

--- a/output/2026-10-01_02_Malesia_Kedah_Componentistica_Ventilazione_industriale.xlsx
+++ b/output/2026-10-01_02_Malesia_Kedah_Componentistica_Ventilazione_industriale.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fornitore filtri polvere (dust filters) e sistemi di aspirazione polveri confermato da fonti terze; settore misto agro-industriale.</t>
+          <t>Fornitore filtri polvere (dust filters) e sistemi di aspirazione polveri confermato da fonti terze; settore misto agro-industriale. [DUPLICATO — vedi anche: 2026-09-30_23_Malesia_Kedah_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
